--- a/tiflow-erezept/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERP-PR-Task.xlsx
+++ b/tiflow-erezept/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERP-PR-Task.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4939" uniqueCount="689">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4956" uniqueCount="701">
   <si>
     <t>Property</t>
   </si>
@@ -120,7 +120,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://gematik.de/fhir/tiflow/StructureDefinition/ti-task</t>
+    <t>https://gematik.de/fhir/tiflow/StructureDefinition/tiflow-order-task</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -502,6 +502,16 @@
     <t>Meta.security</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>CV</t>
+  </si>
+  <si>
+    <t>CE/CNE/CWE subset one of the sets of component 1-3 or 4-6</t>
+  </si>
+  <si>
     <t>Task.meta.tag</t>
   </si>
   <si>
@@ -630,9 +640,6 @@
     <t>An Extension</t>
   </si>
   <si>
-    <t>Erweiterungen für die Aufgabe, die durch url unterschieden werden.</t>
-  </si>
-  <si>
     <t>DomainResource.extension</t>
   </si>
   <si>
@@ -646,10 +653,6 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t>Task.extension:lastMedicationDispense</t>
   </si>
   <si>
@@ -763,9 +766,6 @@
 </t>
   </si>
   <si>
-    <t>Die Task-Ressource enthält zwei Kennungen. Die erste ist die Kennung für den Task, die einen Vorgang im TIFlow darstellt. Die andere Kennung repräsentiert den Patienten als Eigentümer des Vorgangs via Krankenversichertennummer (KVNR)</t>
-  </si>
-  <si>
     <t>Request.identifier, Event.identifier</t>
   </si>
   <si>
@@ -773,6 +773,35 @@
   </si>
   <si>
     <t>FiveWs.identifier</t>
+  </si>
+  <si>
+    <t>CX / EI (occasionally, more often EI maps to a resource id or a URL)</t>
+  </si>
+  <si>
+    <t>Task.identifier:AccessCode</t>
+  </si>
+  <si>
+    <t>AccessCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier {https://gematik.de/fhir/ti/StructureDefinition/tiflow-access-code}
+</t>
+  </si>
+  <si>
+    <t>AccessCode Identifier</t>
+  </si>
+  <si>
+    <t>Generiert vom TI-Flow-Fachdienst. Dieser Identifikator muss in jeder Anfrage zur Task Ressource übertragen werden.</t>
+  </si>
+  <si>
+    <t>Task.identifier:Secret</t>
+  </si>
+  <si>
+    <t>Secret</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier {https://gematik.de/fhir/ti/StructureDefinition/tiflow-secret}
+</t>
   </si>
   <si>
     <t>Task.identifier:PrescriptionID</t>
@@ -791,32 +820,6 @@
     <t>Die E-Rezept-ID ist der Hauptidentifikator für die Task Ressource und den gesamten TIFlow Workflow. Dieser Identifikator wird vom TI-Flow-Fachdienst generiert und darf nicht manuell geändert werden.</t>
   </si>
   <si>
-    <t>Task.identifier:AccessCode</t>
-  </si>
-  <si>
-    <t>AccessCode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier {https://gematik.de/fhir/erp/StructureDefinition/GEM_ERP_PR_AccessCode}
-</t>
-  </si>
-  <si>
-    <t>AccessCode Identifier</t>
-  </si>
-  <si>
-    <t>Generiert vom TI-Flow-Fachdienst. Dieser Identifikator muss in jeder Anfrage zur Task Ressource übertragen werden.</t>
-  </si>
-  <si>
-    <t>Task.identifier:Secret</t>
-  </si>
-  <si>
-    <t>Secret</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier {https://gematik.de/fhir/erp/StructureDefinition/GEM_ERP_PR_Secret}
-</t>
-  </si>
-  <si>
     <t>Task.instantiatesCanonical</t>
   </si>
   <si>
@@ -830,6 +833,9 @@
     <t>The URL pointing to a *FHIR*-defined protocol, guideline, orderset or other definition that is adhered to in whole or in part by this Task.</t>
   </si>
   <si>
+    <t>see [Canonical References](http://hl7.org/fhir/R4/references.html#canonical)</t>
+  </si>
+  <si>
     <t>Enables a formal definition of how he task is to be performed, enabling automation.</t>
   </si>
   <si>
@@ -843,6 +849,9 @@
   </si>
   <si>
     <t>The URL pointing to an *externally* maintained  protocol, guideline, orderset or other definition that is adhered to in whole or in part by this Task.</t>
+  </si>
+  <si>
+    <t>see http://en.wikipedia.org/wiki/Uniform_resource_identifier</t>
   </si>
   <si>
     <t>Enables a formal definition of how he task is to be performed (e.g. using BPMN, BPEL, XPDL or other formal notation to be associated with a task), enabling automation.</t>
@@ -864,6 +873,13 @@
     <t>BasedOn refers to a higher-level authorization that triggered the creation of the task.  It references a "request" resource such as a ServiceRequest, MedicationRequest, ServiceRequest, CarePlan, etc. which is distinct from the "request" resource the task is seeking to fulfill.  This latter resource is referenced by FocusOn.  For example, based on a ServiceRequest (= BasedOn), a task is created to fulfill a procedureRequest ( = FocusOn ) to collect a specimen from a patient.</t>
   </si>
   <si>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
+  </si>
+  <si>
     <t>Request.basedOn, Event.basedOn</t>
   </si>
   <si>
@@ -916,7 +932,7 @@
     <t>Task.status</t>
   </si>
   <si>
-    <t>draft | requested | received | accepted | +</t>
+    <t>draft | ready | on-hold | in-progress | completed | cancelled</t>
   </si>
   <si>
     <t>The current status of the task.</t>
@@ -928,7 +944,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/task-status|4.0.1</t>
+    <t>https://gematik.de/fhir/tiflow/ValueSet/tiflow-order-task-status-vs</t>
   </si>
   <si>
     <t>Request.status, Event.status</t>
@@ -962,6 +978,9 @@
     <t>.inboundRelationship[typeCode=SUBJ].source[classCode=CACT, moodCode=EVN, code="status change"].reasonCode</t>
   </si>
   <si>
+    <t>CE/CNE/CWE</t>
+  </si>
+  <si>
     <t>Task.businessStatus</t>
   </si>
   <si>
@@ -969,6 +988,9 @@
   </si>
   <si>
     <t>Contains business-specific nuances of the business state.</t>
+  </si>
+  <si>
+    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
   </si>
   <si>
     <t>There's often a need to track substates of a task - this is often variable by specific workflow implementation.</t>
@@ -1075,6 +1097,9 @@
   </si>
   <si>
     <t>A free-text description of what is to be performed.</t>
+  </si>
+  <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
   </si>
   <si>
     <t>.text</t>
@@ -1248,6 +1273,14 @@
     <t>Identifies the time action was first taken against the task (start) and/or the time final action was taken against the task prior to marking it as completed (end).</t>
   </si>
   <si>
+    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
+Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
+  </si>
+  <si>
     <t>Event.occurrence[x]</t>
   </si>
   <si>
@@ -1255,6 +1288,9 @@
   </si>
   <si>
     <t>FiveWs.done[x]</t>
+  </si>
+  <si>
+    <t>DR</t>
   </si>
   <si>
     <t>Task.authoredOn</t>
@@ -1382,7 +1418,7 @@
     <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
   </si>
   <si>
-    <t>https://gematik.de/fhir/tiflow-erezept/ValueSet/tiflow-rx-task-organizations-vs</t>
+    <t>https://gematik.de/fhir/erp/ValueSet/GEM_ERP_VS_AvailabilityStatus</t>
   </si>
   <si>
     <t>CodeableConcept.coding</t>
@@ -1547,6 +1583,9 @@
   </si>
   <si>
     <t>Free-text information captured about the task as it progresses.</t>
+  </si>
+  <si>
+    <t>For systems that do not have structured annotations, they can simply communicate a single annotation with no author or time.  This element may need to be included in narrative because of the potential for modifying information.  *Annotations SHOULD NOT* be used to communicate "modifying" information that could be computable. (This is a SHOULD because enforcing user behavior is nearly impossible).</t>
   </si>
   <si>
     <t>Request.note, Event.note</t>
@@ -2504,10 +2543,10 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="145.00390625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="61.83984375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="55.69140625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="20.2734375" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="192.91796875" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
@@ -2517,7 +2556,7 @@
     <col min="37" max="37" width="47.7734375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="94.296875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="39.109375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="53.91015625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3206,7 +3245,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
         <v>118</v>
       </c>
@@ -3225,7 +3264,7 @@
         <v>88</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>78</v>
@@ -3320,7 +3359,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
         <v>123</v>
       </c>
@@ -3339,7 +3378,7 @@
         <v>88</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I8" t="s" s="2">
         <v>78</v>
@@ -3874,7 +3913,7 @@
         <v>80</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>100</v>
@@ -3883,21 +3922,21 @@
         <v>78</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>78</v>
+        <v>157</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>78</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3923,13 +3962,13 @@
         <v>148</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3955,13 +3994,13 @@
         <v>78</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>78</v>
@@ -3979,7 +4018,7 @@
         <v>78</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
@@ -3988,7 +4027,7 @@
         <v>80</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>100</v>
@@ -3997,21 +4036,21 @@
         <v>78</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>78</v>
+        <v>157</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>78</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4037,13 +4076,13 @@
         <v>130</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -4093,7 +4132,7 @@
         <v>78</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -4122,10 +4161,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4148,16 +4187,16 @@
         <v>78</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -4183,13 +4222,13 @@
         <v>78</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>78</v>
@@ -4207,7 +4246,7 @@
         <v>78</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -4236,14 +4275,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -4262,16 +4301,16 @@
         <v>78</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4321,7 +4360,7 @@
         <v>78</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -4339,7 +4378,7 @@
         <v>78</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>78</v>
@@ -4350,14 +4389,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4376,16 +4415,16 @@
         <v>78</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4435,7 +4474,7 @@
         <v>78</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -4453,7 +4492,7 @@
         <v>78</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>78</v>
@@ -4464,10 +4503,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4493,10 +4532,10 @@
         <v>109</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4538,7 +4577,7 @@
         <v>113</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>197</v>
+        <v>114</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>78</v>
@@ -4547,7 +4586,7 @@
         <v>142</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -4576,13 +4615,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>78</v>
@@ -4604,13 +4643,13 @@
         <v>78</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4661,7 +4700,7 @@
         <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -4670,7 +4709,7 @@
         <v>80</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>202</v>
+        <v>78</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>117</v>
@@ -4690,13 +4729,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>78</v>
@@ -4718,13 +4757,13 @@
         <v>78</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4775,7 +4814,7 @@
         <v>78</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -4804,13 +4843,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>78</v>
@@ -4832,13 +4871,13 @@
         <v>78</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4889,7 +4928,7 @@
         <v>78</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4918,13 +4957,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>78</v>
@@ -4946,13 +4985,13 @@
         <v>78</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -5003,7 +5042,7 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -5032,13 +5071,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>78</v>
@@ -5060,13 +5099,13 @@
         <v>78</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -5117,7 +5156,7 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -5146,13 +5185,13 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>78</v>
@@ -5174,13 +5213,13 @@
         <v>78</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -5231,7 +5270,7 @@
         <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -5260,10 +5299,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5289,16 +5328,16 @@
         <v>109</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N25" t="s" s="2">
         <v>112</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>78</v>
@@ -5335,19 +5374,19 @@
         <v>78</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -5365,7 +5404,7 @@
         <v>78</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>78</v>
@@ -5376,10 +5415,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5402,13 +5441,13 @@
         <v>78</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5447,11 +5486,9 @@
         <v>78</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="AC26" t="s" s="2">
         <v>238</v>
       </c>
+      <c r="AC26" s="2"/>
       <c r="AD26" t="s" s="2">
         <v>78</v>
       </c>
@@ -5459,7 +5496,7 @@
         <v>115</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -5468,7 +5505,7 @@
         <v>80</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>100</v>
@@ -5483,25 +5520,25 @@
         <v>241</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>78</v>
+        <v>242</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>88</v>
@@ -5516,13 +5553,13 @@
         <v>78</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5573,7 +5610,7 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -5582,7 +5619,7 @@
         <v>80</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>100</v>
@@ -5597,18 +5634,18 @@
         <v>241</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>78</v>
+        <v>242</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>78</v>
@@ -5630,13 +5667,13 @@
         <v>78</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="L28" t="s" s="2">
-        <v>250</v>
-      </c>
       <c r="M28" t="s" s="2">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5687,7 +5724,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5696,7 +5733,7 @@
         <v>80</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>100</v>
@@ -5711,31 +5748,31 @@
         <v>241</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>78</v>
+        <v>242</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="C29" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="C29" t="s" s="2">
-        <v>253</v>
       </c>
       <c r="D29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>78</v>
@@ -5744,13 +5781,13 @@
         <v>78</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="L29" t="s" s="2">
-        <v>253</v>
-      </c>
       <c r="M29" t="s" s="2">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5801,7 +5838,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5810,7 +5847,7 @@
         <v>80</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>100</v>
@@ -5825,15 +5862,15 @@
         <v>241</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>78</v>
+        <v>242</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5856,17 +5893,19 @@
         <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>259</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="O30" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>78</v>
@@ -5915,7 +5954,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5930,10 +5969,10 @@
         <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>78</v>
@@ -5944,10 +5983,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5973,14 +6012,16 @@
         <v>130</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>265</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>266</v>
+      </c>
       <c r="O31" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>78</v>
@@ -6029,7 +6070,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -6044,10 +6085,10 @@
         <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>78</v>
@@ -6058,10 +6099,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6084,15 +6125,17 @@
         <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>78</v>
@@ -6141,7 +6184,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -6150,16 +6193,16 @@
         <v>80</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>100</v>
+        <v>274</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>78</v>
@@ -6170,10 +6213,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6196,17 +6239,17 @@
         <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>78</v>
@@ -6255,7 +6298,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -6264,30 +6307,30 @@
         <v>88</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>78</v>
+        <v>242</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6310,19 +6353,19 @@
         <v>89</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>78</v>
@@ -6371,7 +6414,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -6380,16 +6423,16 @@
         <v>80</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>100</v>
+        <v>274</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>78</v>
@@ -6398,12 +6441,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6417,7 +6460,7 @@
         <v>88</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>89</v>
@@ -6426,17 +6469,17 @@
         <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>78</v>
@@ -6461,31 +6504,29 @@
         <v>78</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="Y35" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF35" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AA35" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>88</v>
@@ -6500,13 +6541,13 @@
         <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>78</v>
@@ -6514,10 +6555,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6540,16 +6581,16 @@
         <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6575,32 +6616,32 @@
         <v>78</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="Y36" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF36" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="Z36" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA36" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB36" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC36" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD36" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE36" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF36" t="s" s="2">
-        <v>295</v>
-      </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
       </c>
@@ -6608,7 +6649,7 @@
         <v>88</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>100</v>
@@ -6617,21 +6658,21 @@
         <v>78</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>78</v>
+        <v>307</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6654,17 +6695,19 @@
         <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>310</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>311</v>
+      </c>
       <c r="O37" t="s" s="2">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>78</v>
@@ -6689,10 +6732,10 @@
         <v>78</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="Z37" t="s" s="2">
         <v>78</v>
@@ -6713,7 +6756,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6722,7 +6765,7 @@
         <v>88</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>100</v>
@@ -6731,21 +6774,21 @@
         <v>78</v>
       </c>
       <c r="AL37" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6768,16 +6811,16 @@
         <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6785,7 +6828,7 @@
       </c>
       <c r="Q38" s="2"/>
       <c r="R38" t="s" s="2">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="S38" t="s" s="2">
         <v>78</v>
@@ -6803,13 +6846,13 @@
         <v>78</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>78</v>
@@ -6827,7 +6870,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>88</v>
@@ -6842,13 +6885,13 @@
         <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>78</v>
@@ -6856,10 +6899,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6882,23 +6925,23 @@
         <v>78</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q39" t="s" s="2">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="R39" t="s" s="2">
         <v>78</v>
@@ -6919,13 +6962,13 @@
         <v>78</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>78</v>
@@ -6943,7 +6986,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6958,13 +7001,13 @@
         <v>100</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>78</v>
@@ -6972,10 +7015,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6998,16 +7041,16 @@
         <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7033,13 +7076,13 @@
         <v>78</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>78</v>
@@ -7057,7 +7100,7 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -7066,30 +7109,30 @@
         <v>88</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>78</v>
+        <v>307</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7115,12 +7158,14 @@
         <v>102</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>346</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>347</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>78</v>
@@ -7169,7 +7214,7 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -7187,7 +7232,7 @@
         <v>78</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>78</v>
@@ -7198,10 +7243,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7224,19 +7269,19 @@
         <v>89</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>78</v>
@@ -7285,7 +7330,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -7294,34 +7339,34 @@
         <v>88</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>100</v>
+        <v>274</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7331,7 +7376,7 @@
         <v>88</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>78</v>
@@ -7340,17 +7385,19 @@
         <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="O43" t="s" s="2">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>78</v>
@@ -7399,7 +7446,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -7408,19 +7455,19 @@
         <v>88</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>100</v>
+        <v>274</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>78</v>
@@ -7428,10 +7475,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7540,10 +7587,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7654,10 +7701,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7683,13 +7730,13 @@
         <v>102</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7739,7 +7786,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7748,7 +7795,7 @@
         <v>88</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>100</v>
@@ -7757,7 +7804,7 @@
         <v>78</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>78</v>
@@ -7768,10 +7815,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7797,13 +7844,13 @@
         <v>130</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7832,10 +7879,10 @@
         <v>152</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>78</v>
@@ -7853,7 +7900,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7871,7 +7918,7 @@
         <v>78</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>78</v>
@@ -7880,12 +7927,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7899,7 +7946,7 @@
         <v>88</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>78</v>
@@ -7908,16 +7955,16 @@
         <v>89</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7967,7 +8014,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7976,7 +8023,7 @@
         <v>88</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>100</v>
@@ -7985,21 +8032,21 @@
         <v>78</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>78</v>
+        <v>242</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8025,13 +8072,13 @@
         <v>102</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8081,7 +8128,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -8099,7 +8146,7 @@
         <v>78</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>78</v>
@@ -8110,10 +8157,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8136,17 +8183,19 @@
         <v>89</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>393</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="O50" t="s" s="2">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>78</v>
@@ -8195,7 +8244,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -8204,19 +8253,19 @@
         <v>88</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>100</v>
+        <v>274</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>78</v>
@@ -8224,10 +8273,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8250,15 +8299,17 @@
         <v>89</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>401</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>402</v>
+      </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>78</v>
@@ -8307,7 +8358,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -8316,34 +8367,34 @@
         <v>88</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>100</v>
+        <v>403</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>78</v>
+        <v>407</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8362,17 +8413,17 @@
         <v>78</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>78</v>
@@ -8421,7 +8472,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -8430,19 +8481,19 @@
         <v>88</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>403</v>
+        <v>414</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>404</v>
+        <v>415</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>405</v>
+        <v>416</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>406</v>
+        <v>417</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>78</v>
@@ -8450,14 +8501,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>407</v>
+        <v>418</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>407</v>
+        <v>418</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8476,17 +8527,17 @@
         <v>89</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>410</v>
+        <v>421</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>411</v>
+        <v>422</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>78</v>
@@ -8535,7 +8586,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>407</v>
+        <v>418</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8544,7 +8595,7 @@
         <v>88</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>403</v>
+        <v>414</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>100</v>
@@ -8553,7 +8604,7 @@
         <v>78</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>78</v>
@@ -8564,10 +8615,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>413</v>
+        <v>424</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>413</v>
+        <v>424</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8590,17 +8641,19 @@
         <v>89</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>414</v>
+        <v>425</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>415</v>
+        <v>426</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>427</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="O54" t="s" s="2">
-        <v>417</v>
+        <v>428</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>78</v>
@@ -8649,7 +8702,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>413</v>
+        <v>424</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8658,19 +8711,19 @@
         <v>88</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>100</v>
+        <v>274</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>418</v>
+        <v>429</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>420</v>
+        <v>431</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>78</v>
@@ -8678,10 +8731,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>421</v>
+        <v>432</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>421</v>
+        <v>432</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8704,17 +8757,19 @@
         <v>78</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>422</v>
+        <v>433</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>434</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>311</v>
+      </c>
       <c r="O55" t="s" s="2">
-        <v>424</v>
+        <v>435</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>78</v>
@@ -8739,13 +8794,13 @@
         <v>78</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>426</v>
+        <v>437</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>78</v>
@@ -8763,7 +8818,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>421</v>
+        <v>432</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8772,30 +8827,30 @@
         <v>80</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>78</v>
+        <v>307</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8904,10 +8959,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9018,10 +9073,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>432</v>
+        <v>443</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>432</v>
+        <v>443</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9047,16 +9102,16 @@
         <v>148</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>433</v>
+        <v>444</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>434</v>
+        <v>445</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>436</v>
+        <v>447</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>78</v>
@@ -9081,11 +9136,11 @@
         <v>78</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="Y58" s="2"/>
       <c r="Z58" t="s" s="2">
-        <v>437</v>
+        <v>448</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>78</v>
@@ -9103,7 +9158,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>438</v>
+        <v>449</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -9112,7 +9167,7 @@
         <v>80</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>100</v>
@@ -9121,21 +9176,21 @@
         <v>78</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>439</v>
+        <v>450</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>440</v>
+        <v>451</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>441</v>
+        <v>452</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>441</v>
+        <v>452</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9161,16 +9216,16 @@
         <v>102</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>442</v>
+        <v>453</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>443</v>
+        <v>454</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>444</v>
+        <v>455</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>445</v>
+        <v>456</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>78</v>
@@ -9219,7 +9274,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>446</v>
+        <v>457</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -9237,25 +9292,25 @@
         <v>78</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>448</v>
+        <v>459</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>449</v>
+        <v>460</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>449</v>
+        <v>460</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>450</v>
+        <v>461</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9274,19 +9329,19 @@
         <v>89</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>451</v>
+        <v>462</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>452</v>
+        <v>463</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>454</v>
+        <v>465</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>455</v>
+        <v>466</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>78</v>
@@ -9335,7 +9390,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>449</v>
+        <v>460</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9344,19 +9399,19 @@
         <v>88</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>100</v>
+        <v>274</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>456</v>
+        <v>467</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>457</v>
+        <v>468</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>78</v>
@@ -9364,10 +9419,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>458</v>
+        <v>469</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>458</v>
+        <v>469</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9390,17 +9445,19 @@
         <v>89</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>459</v>
+        <v>470</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>460</v>
+        <v>471</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>472</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="O61" t="s" s="2">
-        <v>462</v>
+        <v>473</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>78</v>
@@ -9449,7 +9506,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>458</v>
+        <v>469</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9458,19 +9515,19 @@
         <v>88</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>100</v>
+        <v>274</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>463</v>
+        <v>474</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>464</v>
+        <v>475</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>465</v>
+        <v>476</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>78</v>
@@ -9478,10 +9535,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>466</v>
+        <v>477</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>466</v>
+        <v>477</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9504,16 +9561,16 @@
         <v>78</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>467</v>
+        <v>478</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>468</v>
+        <v>479</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>469</v>
+        <v>480</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9539,10 +9596,10 @@
         <v>78</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>470</v>
+        <v>481</v>
       </c>
       <c r="Z62" t="s" s="2">
         <v>78</v>
@@ -9563,7 +9620,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>466</v>
+        <v>477</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9572,30 +9629,30 @@
         <v>88</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>471</v>
+        <v>482</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>472</v>
+        <v>483</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>473</v>
+        <v>484</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>474</v>
+        <v>485</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>475</v>
+        <v>486</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>475</v>
+        <v>486</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9618,16 +9675,16 @@
         <v>78</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>467</v>
+        <v>478</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>476</v>
+        <v>487</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>477</v>
+        <v>488</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9677,7 +9734,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>475</v>
+        <v>486</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9686,19 +9743,19 @@
         <v>88</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>100</v>
+        <v>274</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>478</v>
+        <v>489</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>479</v>
+        <v>490</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>473</v>
+        <v>484</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>78</v>
@@ -9706,10 +9763,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>480</v>
+        <v>491</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>480</v>
+        <v>491</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9732,15 +9789,17 @@
         <v>78</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>481</v>
+        <v>492</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>482</v>
+        <v>493</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="N64" s="2"/>
+        <v>494</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>78</v>
@@ -9789,7 +9848,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>480</v>
+        <v>491</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9798,30 +9857,30 @@
         <v>80</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>100</v>
+        <v>274</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>486</v>
+        <v>497</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>487</v>
+        <v>498</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>487</v>
+        <v>498</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9844,15 +9903,17 @@
         <v>78</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>488</v>
+        <v>499</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>489</v>
+        <v>500</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>501</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>502</v>
+      </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>78</v>
@@ -9901,7 +9962,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>487</v>
+        <v>498</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9910,34 +9971,34 @@
         <v>80</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>491</v>
+        <v>503</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>492</v>
+        <v>504</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>78</v>
+        <v>196</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>494</v>
+        <v>506</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9956,16 +10017,16 @@
         <v>78</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>495</v>
+        <v>507</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>496</v>
+        <v>508</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>497</v>
+        <v>509</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10015,7 +10076,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -10024,16 +10085,16 @@
         <v>80</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>100</v>
+        <v>274</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>499</v>
+        <v>511</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>500</v>
+        <v>512</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>78</v>
@@ -10044,10 +10105,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10070,17 +10131,17 @@
         <v>78</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>505</v>
+        <v>517</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>78</v>
@@ -10129,7 +10190,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -10138,7 +10199,7 @@
         <v>88</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>100</v>
@@ -10147,7 +10208,7 @@
         <v>78</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>78</v>
@@ -10158,10 +10219,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10270,10 +10331,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>508</v>
+        <v>520</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>508</v>
+        <v>520</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10343,16 +10404,16 @@
         <v>78</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC69" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF69" t="s" s="2">
         <v>116</v>
@@ -10384,14 +10445,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>509</v>
+        <v>521</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>509</v>
+        <v>521</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10413,16 +10474,16 @@
         <v>109</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="N70" t="s" s="2">
         <v>112</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>78</v>
@@ -10471,7 +10532,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>513</v>
+        <v>525</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10489,7 +10550,7 @@
         <v>78</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>78</v>
@@ -10500,10 +10561,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10526,17 +10587,17 @@
         <v>78</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>516</v>
+        <v>528</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>518</v>
+        <v>530</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>78</v>
@@ -10585,7 +10646,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10603,7 +10664,7 @@
         <v>78</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>78</v>
@@ -10614,10 +10675,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10640,19 +10701,19 @@
         <v>78</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>521</v>
+        <v>533</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>522</v>
+        <v>534</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>524</v>
+        <v>536</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>78</v>
@@ -10701,7 +10762,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10710,30 +10771,30 @@
         <v>88</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>100</v>
+        <v>403</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>525</v>
+        <v>537</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>78</v>
+        <v>407</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>526</v>
+        <v>538</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>526</v>
+        <v>538</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10756,15 +10817,17 @@
         <v>78</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>527</v>
+        <v>539</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>528</v>
+        <v>540</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="N73" s="2"/>
+        <v>541</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>78</v>
@@ -10813,7 +10876,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>526</v>
+        <v>538</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10822,16 +10885,16 @@
         <v>80</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>100</v>
+        <v>274</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>530</v>
+        <v>542</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>78</v>
@@ -10842,14 +10905,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>531</v>
+        <v>543</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>531</v>
+        <v>543</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>532</v>
+        <v>544</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10868,17 +10931,17 @@
         <v>78</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>533</v>
+        <v>545</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>534</v>
+        <v>546</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>535</v>
+        <v>547</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>78</v>
@@ -10915,7 +10978,7 @@
         <v>78</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>536</v>
+        <v>548</v>
       </c>
       <c r="AC74" s="2"/>
       <c r="AD74" t="s" s="2">
@@ -10925,7 +10988,7 @@
         <v>142</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>531</v>
+        <v>543</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10934,7 +10997,7 @@
         <v>80</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>100</v>
@@ -10943,7 +11006,7 @@
         <v>78</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>537</v>
+        <v>549</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>78</v>
@@ -10954,10 +11017,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11066,10 +11129,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>539</v>
+        <v>551</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>539</v>
+        <v>551</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11139,16 +11202,16 @@
         <v>78</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF76" t="s" s="2">
         <v>116</v>
@@ -11180,14 +11243,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11209,16 +11272,16 @@
         <v>109</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="N77" t="s" s="2">
         <v>112</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>78</v>
@@ -11267,7 +11330,7 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>513</v>
+        <v>525</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -11285,7 +11348,7 @@
         <v>78</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>78</v>
@@ -11296,14 +11359,14 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>541</v>
+        <v>553</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>541</v>
+        <v>553</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -11322,19 +11385,19 @@
         <v>78</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>543</v>
+        <v>555</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>545</v>
+        <v>557</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>78</v>
@@ -11359,10 +11422,10 @@
         <v>78</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>547</v>
+        <v>559</v>
       </c>
       <c r="Z78" t="s" s="2">
         <v>78</v>
@@ -11383,7 +11446,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>541</v>
+        <v>553</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>88</v>
@@ -11392,7 +11455,7 @@
         <v>88</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>100</v>
@@ -11401,21 +11464,21 @@
         <v>78</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>537</v>
+        <v>549</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>78</v>
+        <v>307</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>548</v>
+        <v>560</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>548</v>
+        <v>560</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11438,13 +11501,13 @@
         <v>78</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>549</v>
+        <v>561</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>550</v>
+        <v>562</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>551</v>
+        <v>563</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11495,7 +11558,7 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>548</v>
+        <v>560</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>88</v>
@@ -11504,7 +11567,7 @@
         <v>88</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>100</v>
@@ -11513,7 +11576,7 @@
         <v>78</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>537</v>
+        <v>549</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>78</v>
@@ -11524,16 +11587,16 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>552</v>
+        <v>564</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>531</v>
+        <v>543</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>553</v>
+        <v>565</v>
       </c>
       <c r="D80" t="s" s="2">
-        <v>532</v>
+        <v>544</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -11552,17 +11615,17 @@
         <v>78</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>554</v>
+        <v>566</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>555</v>
+        <v>567</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
-        <v>535</v>
+        <v>547</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>78</v>
@@ -11611,7 +11674,7 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>531</v>
+        <v>543</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11620,7 +11683,7 @@
         <v>80</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ80" t="s" s="2">
         <v>100</v>
@@ -11629,7 +11692,7 @@
         <v>78</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>537</v>
+        <v>549</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>78</v>
@@ -11640,10 +11703,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>556</v>
+        <v>568</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11752,10 +11815,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>557</v>
+        <v>569</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>539</v>
+        <v>551</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11825,16 +11888,16 @@
         <v>78</v>
       </c>
       <c r="AB82" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC82" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF82" t="s" s="2">
         <v>116</v>
@@ -11866,14 +11929,14 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>558</v>
+        <v>570</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -11895,16 +11958,16 @@
         <v>109</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>112</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>78</v>
@@ -11953,7 +12016,7 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>513</v>
+        <v>525</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -11971,7 +12034,7 @@
         <v>78</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>78</v>
@@ -11982,14 +12045,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>559</v>
+        <v>571</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>541</v>
+        <v>553</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -12008,19 +12071,19 @@
         <v>78</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>543</v>
+        <v>555</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>545</v>
+        <v>557</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>78</v>
@@ -12045,10 +12108,10 @@
         <v>78</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>547</v>
+        <v>559</v>
       </c>
       <c r="Z84" t="s" s="2">
         <v>78</v>
@@ -12069,7 +12132,7 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>541</v>
+        <v>553</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>88</v>
@@ -12078,7 +12141,7 @@
         <v>88</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>100</v>
@@ -12087,21 +12150,21 @@
         <v>78</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>537</v>
+        <v>549</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>78</v>
+        <v>307</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>560</v>
+        <v>572</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12210,10 +12273,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>562</v>
+        <v>574</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>563</v>
+        <v>575</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12324,10 +12387,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>564</v>
+        <v>576</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>565</v>
+        <v>577</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12353,16 +12416,16 @@
         <v>148</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>433</v>
+        <v>444</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>434</v>
+        <v>445</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>436</v>
+        <v>447</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>78</v>
@@ -12387,11 +12450,11 @@
         <v>78</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="Y87" s="2"/>
       <c r="Z87" t="s" s="2">
-        <v>566</v>
+        <v>578</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>78</v>
@@ -12409,7 +12472,7 @@
         <v>78</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>438</v>
+        <v>449</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -12418,7 +12481,7 @@
         <v>80</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>100</v>
@@ -12427,21 +12490,21 @@
         <v>78</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>439</v>
+        <v>450</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>440</v>
+        <v>451</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>567</v>
+        <v>579</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>568</v>
+        <v>580</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12550,10 +12613,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>569</v>
+        <v>581</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>570</v>
+        <v>582</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12664,10 +12727,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>571</v>
+        <v>583</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>572</v>
+        <v>584</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12693,16 +12756,16 @@
         <v>130</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>573</v>
+        <v>585</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>574</v>
+        <v>586</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>575</v>
+        <v>587</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>78</v>
@@ -12751,7 +12814,7 @@
         <v>78</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>577</v>
+        <v>589</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -12769,21 +12832,21 @@
         <v>78</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>578</v>
+        <v>590</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>579</v>
+        <v>591</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>580</v>
+        <v>592</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>581</v>
+        <v>593</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12809,13 +12872,13 @@
         <v>102</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>582</v>
+        <v>594</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>583</v>
+        <v>595</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>584</v>
+        <v>596</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -12865,7 +12928,7 @@
         <v>78</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>585</v>
+        <v>597</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -12883,21 +12946,21 @@
         <v>78</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>586</v>
+        <v>598</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>587</v>
+        <v>599</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>588</v>
+        <v>600</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>589</v>
+        <v>601</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12920,17 +12983,17 @@
         <v>89</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>590</v>
+        <v>602</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>591</v>
+        <v>603</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" t="s" s="2">
-        <v>592</v>
+        <v>604</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>78</v>
@@ -12979,7 +13042,7 @@
         <v>78</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>593</v>
+        <v>605</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -12997,21 +13060,21 @@
         <v>78</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>594</v>
+        <v>606</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>595</v>
+        <v>607</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>596</v>
+        <v>608</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>597</v>
+        <v>609</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13037,14 +13100,16 @@
         <v>102</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>598</v>
+        <v>610</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="N93" s="2"/>
+        <v>611</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>347</v>
+      </c>
       <c r="O93" t="s" s="2">
-        <v>600</v>
+        <v>612</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>78</v>
@@ -13093,7 +13158,7 @@
         <v>78</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>601</v>
+        <v>613</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -13111,21 +13176,21 @@
         <v>78</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>602</v>
+        <v>614</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>603</v>
+        <v>615</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>604</v>
+        <v>616</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>605</v>
+        <v>617</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13148,19 +13213,19 @@
         <v>89</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>606</v>
+        <v>618</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>607</v>
+        <v>619</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>608</v>
+        <v>620</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>609</v>
+        <v>621</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>610</v>
+        <v>622</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>78</v>
@@ -13209,7 +13274,7 @@
         <v>78</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>611</v>
+        <v>623</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -13227,21 +13292,21 @@
         <v>78</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>612</v>
+        <v>624</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>613</v>
+        <v>625</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>614</v>
+        <v>626</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>615</v>
+        <v>627</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13267,16 +13332,16 @@
         <v>102</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>442</v>
+        <v>453</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>443</v>
+        <v>454</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>444</v>
+        <v>455</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>445</v>
+        <v>456</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>78</v>
@@ -13325,7 +13390,7 @@
         <v>78</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>446</v>
+        <v>457</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -13343,21 +13408,21 @@
         <v>78</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>448</v>
+        <v>459</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>616</v>
+        <v>628</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>548</v>
+        <v>560</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13380,13 +13445,13 @@
         <v>78</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>617</v>
+        <v>629</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>550</v>
+        <v>562</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>551</v>
+        <v>563</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13437,7 +13502,7 @@
         <v>78</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>548</v>
+        <v>560</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>88</v>
@@ -13446,7 +13511,7 @@
         <v>88</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ96" t="s" s="2">
         <v>100</v>
@@ -13455,7 +13520,7 @@
         <v>78</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>537</v>
+        <v>549</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>78</v>
@@ -13466,16 +13531,16 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>618</v>
+        <v>630</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>531</v>
+        <v>543</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="D97" t="s" s="2">
-        <v>532</v>
+        <v>544</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -13494,17 +13559,17 @@
         <v>78</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>620</v>
+        <v>632</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>555</v>
+        <v>567</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" t="s" s="2">
-        <v>535</v>
+        <v>547</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>78</v>
@@ -13553,7 +13618,7 @@
         <v>78</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>531</v>
+        <v>543</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -13562,7 +13627,7 @@
         <v>80</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ97" t="s" s="2">
         <v>100</v>
@@ -13571,7 +13636,7 @@
         <v>78</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>537</v>
+        <v>549</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>78</v>
@@ -13582,10 +13647,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>621</v>
+        <v>633</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13694,10 +13759,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>622</v>
+        <v>634</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>539</v>
+        <v>551</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13767,16 +13832,16 @@
         <v>78</v>
       </c>
       <c r="AB99" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC99" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD99" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE99" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF99" t="s" s="2">
         <v>116</v>
@@ -13808,14 +13873,14 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>623</v>
+        <v>635</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
@@ -13837,16 +13902,16 @@
         <v>109</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="N100" t="s" s="2">
         <v>112</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>78</v>
@@ -13895,7 +13960,7 @@
         <v>78</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>513</v>
+        <v>525</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -13913,7 +13978,7 @@
         <v>78</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>78</v>
@@ -13924,14 +13989,14 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>624</v>
+        <v>636</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>541</v>
+        <v>553</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -13950,19 +14015,19 @@
         <v>78</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>543</v>
+        <v>555</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>545</v>
+        <v>557</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>78</v>
@@ -13987,10 +14052,10 @@
         <v>78</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>547</v>
+        <v>559</v>
       </c>
       <c r="Z101" t="s" s="2">
         <v>78</v>
@@ -14011,7 +14076,7 @@
         <v>78</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>541</v>
+        <v>553</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>88</v>
@@ -14020,7 +14085,7 @@
         <v>88</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ101" t="s" s="2">
         <v>100</v>
@@ -14029,21 +14094,21 @@
         <v>78</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>537</v>
+        <v>549</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>78</v>
+        <v>307</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>625</v>
+        <v>637</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14152,10 +14217,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>626</v>
+        <v>638</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>563</v>
+        <v>575</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14266,10 +14331,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>627</v>
+        <v>639</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>565</v>
+        <v>577</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14295,16 +14360,16 @@
         <v>148</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>433</v>
+        <v>444</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>434</v>
+        <v>445</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>436</v>
+        <v>447</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>78</v>
@@ -14329,11 +14394,11 @@
         <v>78</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="Y104" s="2"/>
       <c r="Z104" t="s" s="2">
-        <v>566</v>
+        <v>578</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>78</v>
@@ -14351,7 +14416,7 @@
         <v>78</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>438</v>
+        <v>449</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -14360,7 +14425,7 @@
         <v>80</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>100</v>
@@ -14369,21 +14434,21 @@
         <v>78</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>439</v>
+        <v>450</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>440</v>
+        <v>451</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>628</v>
+        <v>640</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>568</v>
+        <v>580</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14492,10 +14557,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>629</v>
+        <v>641</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>570</v>
+        <v>582</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14606,10 +14671,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>630</v>
+        <v>642</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>572</v>
+        <v>584</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14635,16 +14700,16 @@
         <v>130</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>573</v>
+        <v>585</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>574</v>
+        <v>586</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>575</v>
+        <v>587</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>78</v>
@@ -14693,7 +14758,7 @@
         <v>78</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>577</v>
+        <v>589</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>79</v>
@@ -14711,21 +14776,21 @@
         <v>78</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>578</v>
+        <v>590</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>579</v>
+        <v>591</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>631</v>
+        <v>643</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>581</v>
+        <v>593</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14751,13 +14816,13 @@
         <v>102</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>582</v>
+        <v>594</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>583</v>
+        <v>595</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>584</v>
+        <v>596</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -14807,7 +14872,7 @@
         <v>78</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>585</v>
+        <v>597</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>79</v>
@@ -14825,21 +14890,21 @@
         <v>78</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>586</v>
+        <v>598</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>587</v>
+        <v>599</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>632</v>
+        <v>644</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>589</v>
+        <v>601</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14862,24 +14927,24 @@
         <v>89</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>590</v>
+        <v>602</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>591</v>
+        <v>603</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" t="s" s="2">
-        <v>592</v>
+        <v>604</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q109" s="2"/>
       <c r="R109" t="s" s="2">
-        <v>633</v>
+        <v>645</v>
       </c>
       <c r="S109" t="s" s="2">
         <v>78</v>
@@ -14921,7 +14986,7 @@
         <v>78</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>593</v>
+        <v>605</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
@@ -14939,21 +15004,21 @@
         <v>78</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>594</v>
+        <v>606</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>595</v>
+        <v>607</v>
       </c>
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>634</v>
+        <v>646</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>597</v>
+        <v>609</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14979,14 +15044,16 @@
         <v>102</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>598</v>
+        <v>610</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="N110" s="2"/>
+        <v>611</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>347</v>
+      </c>
       <c r="O110" t="s" s="2">
-        <v>600</v>
+        <v>612</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>78</v>
@@ -15035,7 +15102,7 @@
         <v>78</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>601</v>
+        <v>613</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -15053,21 +15120,21 @@
         <v>78</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>602</v>
+        <v>614</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>603</v>
+        <v>615</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>635</v>
+        <v>647</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>605</v>
+        <v>617</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15090,19 +15157,19 @@
         <v>89</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>606</v>
+        <v>618</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>607</v>
+        <v>619</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>608</v>
+        <v>620</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>609</v>
+        <v>621</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>610</v>
+        <v>622</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>78</v>
@@ -15151,7 +15218,7 @@
         <v>78</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>611</v>
+        <v>623</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
@@ -15169,21 +15236,21 @@
         <v>78</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>612</v>
+        <v>624</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>613</v>
+        <v>625</v>
       </c>
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>636</v>
+        <v>648</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>615</v>
+        <v>627</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15209,16 +15276,16 @@
         <v>102</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>442</v>
+        <v>453</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>443</v>
+        <v>454</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>444</v>
+        <v>455</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>445</v>
+        <v>456</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>78</v>
@@ -15267,7 +15334,7 @@
         <v>78</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>446</v>
+        <v>457</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
@@ -15285,21 +15352,21 @@
         <v>78</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>448</v>
+        <v>459</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>637</v>
+        <v>649</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>548</v>
+        <v>560</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15322,16 +15389,16 @@
         <v>78</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>638</v>
+        <v>650</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>550</v>
+        <v>562</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>551</v>
+        <v>563</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>639</v>
+        <v>651</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -15381,7 +15448,7 @@
         <v>78</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>548</v>
+        <v>560</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>88</v>
@@ -15390,7 +15457,7 @@
         <v>88</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ113" t="s" s="2">
         <v>100</v>
@@ -15399,7 +15466,7 @@
         <v>78</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>537</v>
+        <v>549</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>78</v>
@@ -15410,10 +15477,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>640</v>
+        <v>652</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>640</v>
+        <v>652</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15436,17 +15503,17 @@
         <v>78</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>641</v>
+        <v>653</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>642</v>
+        <v>654</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" t="s" s="2">
-        <v>643</v>
+        <v>655</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>78</v>
@@ -15483,7 +15550,7 @@
         <v>78</v>
       </c>
       <c r="AB114" t="s" s="2">
-        <v>536</v>
+        <v>548</v>
       </c>
       <c r="AC114" s="2"/>
       <c r="AD114" t="s" s="2">
@@ -15493,7 +15560,7 @@
         <v>142</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>640</v>
+        <v>652</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>79</v>
@@ -15502,7 +15569,7 @@
         <v>80</v>
       </c>
       <c r="AI114" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ114" t="s" s="2">
         <v>100</v>
@@ -15511,7 +15578,7 @@
         <v>78</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>537</v>
+        <v>549</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>78</v>
@@ -15522,10 +15589,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>644</v>
+        <v>656</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>644</v>
+        <v>656</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15634,10 +15701,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>645</v>
+        <v>657</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>645</v>
+        <v>657</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15707,16 +15774,16 @@
         <v>78</v>
       </c>
       <c r="AB116" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC116" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD116" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE116" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF116" t="s" s="2">
         <v>116</v>
@@ -15748,14 +15815,14 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>646</v>
+        <v>658</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>646</v>
+        <v>658</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
@@ -15777,16 +15844,16 @@
         <v>109</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="N117" t="s" s="2">
         <v>112</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>78</v>
@@ -15835,7 +15902,7 @@
         <v>78</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>513</v>
+        <v>525</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>79</v>
@@ -15853,7 +15920,7 @@
         <v>78</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>78</v>
@@ -15864,14 +15931,14 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>647</v>
+        <v>659</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>647</v>
+        <v>659</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
@@ -15890,17 +15957,19 @@
         <v>78</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>648</v>
+        <v>660</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="N118" s="2"/>
+        <v>661</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>311</v>
+      </c>
       <c r="O118" t="s" s="2">
-        <v>650</v>
+        <v>662</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>78</v>
@@ -15925,10 +15994,10 @@
         <v>78</v>
       </c>
       <c r="X118" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="Y118" t="s" s="2">
-        <v>651</v>
+        <v>663</v>
       </c>
       <c r="Z118" t="s" s="2">
         <v>78</v>
@@ -15949,7 +16018,7 @@
         <v>78</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>647</v>
+        <v>659</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>88</v>
@@ -15958,7 +16027,7 @@
         <v>88</v>
       </c>
       <c r="AI118" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ118" t="s" s="2">
         <v>100</v>
@@ -15967,21 +16036,21 @@
         <v>78</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>537</v>
+        <v>549</v>
       </c>
       <c r="AM118" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>78</v>
+        <v>307</v>
       </c>
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>652</v>
+        <v>664</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>652</v>
+        <v>664</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16004,17 +16073,17 @@
         <v>78</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>549</v>
+        <v>561</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>653</v>
+        <v>665</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>654</v>
+        <v>666</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" t="s" s="2">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>78</v>
@@ -16063,7 +16132,7 @@
         <v>78</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>652</v>
+        <v>664</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>88</v>
@@ -16072,7 +16141,7 @@
         <v>88</v>
       </c>
       <c r="AI119" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ119" t="s" s="2">
         <v>100</v>
@@ -16081,7 +16150,7 @@
         <v>78</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>537</v>
+        <v>549</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>78</v>
@@ -16092,13 +16161,13 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>656</v>
+        <v>668</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>640</v>
+        <v>652</v>
       </c>
       <c r="C120" t="s" s="2">
-        <v>657</v>
+        <v>669</v>
       </c>
       <c r="D120" t="s" s="2">
         <v>78</v>
@@ -16120,17 +16189,17 @@
         <v>78</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>658</v>
+        <v>670</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>659</v>
+        <v>671</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" t="s" s="2">
-        <v>643</v>
+        <v>655</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>78</v>
@@ -16179,7 +16248,7 @@
         <v>78</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>640</v>
+        <v>652</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
@@ -16188,7 +16257,7 @@
         <v>80</v>
       </c>
       <c r="AI120" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ120" t="s" s="2">
         <v>100</v>
@@ -16197,7 +16266,7 @@
         <v>78</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>537</v>
+        <v>549</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>78</v>
@@ -16208,10 +16277,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>644</v>
+        <v>656</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16320,10 +16389,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>661</v>
+        <v>673</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>645</v>
+        <v>657</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16393,16 +16462,16 @@
         <v>78</v>
       </c>
       <c r="AB122" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC122" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD122" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE122" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF122" t="s" s="2">
         <v>116</v>
@@ -16434,14 +16503,14 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>662</v>
+        <v>674</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>646</v>
+        <v>658</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
@@ -16463,16 +16532,16 @@
         <v>109</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="N123" t="s" s="2">
         <v>112</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>78</v>
@@ -16521,7 +16590,7 @@
         <v>78</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>513</v>
+        <v>525</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>79</v>
@@ -16539,7 +16608,7 @@
         <v>78</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="AM123" t="s" s="2">
         <v>78</v>
@@ -16550,14 +16619,14 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>663</v>
+        <v>675</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>647</v>
+        <v>659</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
@@ -16576,17 +16645,19 @@
         <v>78</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>648</v>
+        <v>660</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="N124" s="2"/>
+        <v>661</v>
+      </c>
+      <c r="N124" t="s" s="2">
+        <v>311</v>
+      </c>
       <c r="O124" t="s" s="2">
-        <v>650</v>
+        <v>662</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>78</v>
@@ -16611,10 +16682,10 @@
         <v>78</v>
       </c>
       <c r="X124" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="Y124" t="s" s="2">
-        <v>651</v>
+        <v>663</v>
       </c>
       <c r="Z124" t="s" s="2">
         <v>78</v>
@@ -16635,7 +16706,7 @@
         <v>78</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>647</v>
+        <v>659</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>88</v>
@@ -16644,7 +16715,7 @@
         <v>88</v>
       </c>
       <c r="AI124" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ124" t="s" s="2">
         <v>100</v>
@@ -16653,21 +16724,21 @@
         <v>78</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>537</v>
+        <v>549</v>
       </c>
       <c r="AM124" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>78</v>
+        <v>307</v>
       </c>
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>664</v>
+        <v>676</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>665</v>
+        <v>677</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16776,10 +16847,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>666</v>
+        <v>678</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>667</v>
+        <v>679</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16890,10 +16961,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>668</v>
+        <v>680</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16919,16 +16990,16 @@
         <v>148</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>433</v>
+        <v>444</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>434</v>
+        <v>445</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c r="O127" t="s" s="2">
-        <v>436</v>
+        <v>447</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>78</v>
@@ -16953,11 +17024,11 @@
         <v>78</v>
       </c>
       <c r="X127" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="Y127" s="2"/>
       <c r="Z127" t="s" s="2">
-        <v>566</v>
+        <v>578</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>78</v>
@@ -16975,7 +17046,7 @@
         <v>78</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>438</v>
+        <v>449</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>79</v>
@@ -16984,7 +17055,7 @@
         <v>80</v>
       </c>
       <c r="AI127" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ127" t="s" s="2">
         <v>100</v>
@@ -16993,21 +17064,21 @@
         <v>78</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>439</v>
+        <v>450</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>440</v>
+        <v>451</v>
       </c>
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>670</v>
+        <v>682</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>671</v>
+        <v>683</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17116,10 +17187,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>672</v>
+        <v>684</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>673</v>
+        <v>685</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17230,10 +17301,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>674</v>
+        <v>686</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>675</v>
+        <v>687</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17259,16 +17330,16 @@
         <v>130</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>573</v>
+        <v>585</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>574</v>
+        <v>586</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>575</v>
+        <v>587</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>78</v>
@@ -17317,7 +17388,7 @@
         <v>78</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>577</v>
+        <v>589</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>79</v>
@@ -17335,21 +17406,21 @@
         <v>78</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>578</v>
+        <v>590</v>
       </c>
       <c r="AM130" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>579</v>
+        <v>591</v>
       </c>
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>676</v>
+        <v>688</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>677</v>
+        <v>689</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17375,13 +17446,13 @@
         <v>102</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>582</v>
+        <v>594</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>583</v>
+        <v>595</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>584</v>
+        <v>596</v>
       </c>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
@@ -17431,7 +17502,7 @@
         <v>78</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>585</v>
+        <v>597</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>79</v>
@@ -17449,21 +17520,21 @@
         <v>78</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>586</v>
+        <v>598</v>
       </c>
       <c r="AM131" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>587</v>
+        <v>599</v>
       </c>
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>678</v>
+        <v>690</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17486,24 +17557,24 @@
         <v>89</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>590</v>
+        <v>602</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>591</v>
+        <v>603</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" t="s" s="2">
-        <v>592</v>
+        <v>604</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q132" s="2"/>
       <c r="R132" t="s" s="2">
-        <v>680</v>
+        <v>692</v>
       </c>
       <c r="S132" t="s" s="2">
         <v>78</v>
@@ -17545,7 +17616,7 @@
         <v>78</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>593</v>
+        <v>605</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>79</v>
@@ -17563,21 +17634,21 @@
         <v>78</v>
       </c>
       <c r="AL132" t="s" s="2">
-        <v>594</v>
+        <v>606</v>
       </c>
       <c r="AM132" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>595</v>
+        <v>607</v>
       </c>
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>681</v>
+        <v>693</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>682</v>
+        <v>694</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17603,14 +17674,16 @@
         <v>102</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>598</v>
+        <v>610</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="N133" s="2"/>
+        <v>611</v>
+      </c>
+      <c r="N133" t="s" s="2">
+        <v>347</v>
+      </c>
       <c r="O133" t="s" s="2">
-        <v>600</v>
+        <v>612</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>78</v>
@@ -17659,7 +17732,7 @@
         <v>78</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>601</v>
+        <v>613</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>79</v>
@@ -17677,21 +17750,21 @@
         <v>78</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>602</v>
+        <v>614</v>
       </c>
       <c r="AM133" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>603</v>
+        <v>615</v>
       </c>
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>683</v>
+        <v>695</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>684</v>
+        <v>696</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -17714,19 +17787,19 @@
         <v>89</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>606</v>
+        <v>618</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>607</v>
+        <v>619</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>608</v>
+        <v>620</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>609</v>
+        <v>621</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>610</v>
+        <v>622</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>78</v>
@@ -17775,7 +17848,7 @@
         <v>78</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>611</v>
+        <v>623</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
@@ -17793,21 +17866,21 @@
         <v>78</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>612</v>
+        <v>624</v>
       </c>
       <c r="AM134" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>613</v>
+        <v>625</v>
       </c>
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>685</v>
+        <v>697</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>686</v>
+        <v>698</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17833,16 +17906,16 @@
         <v>102</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>442</v>
+        <v>453</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>443</v>
+        <v>454</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>444</v>
+        <v>455</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>445</v>
+        <v>456</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>78</v>
@@ -17891,7 +17964,7 @@
         <v>78</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>446</v>
+        <v>457</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>79</v>
@@ -17909,21 +17982,21 @@
         <v>78</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="AM135" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>448</v>
+        <v>459</v>
       </c>
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>687</v>
+        <v>699</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>652</v>
+        <v>664</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -17946,17 +18019,17 @@
         <v>78</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>688</v>
+        <v>700</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>653</v>
+        <v>665</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>654</v>
+        <v>666</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" t="s" s="2">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>78</v>
@@ -18005,7 +18078,7 @@
         <v>78</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>652</v>
+        <v>664</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>88</v>
@@ -18014,7 +18087,7 @@
         <v>88</v>
       </c>
       <c r="AI136" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ136" t="s" s="2">
         <v>100</v>
@@ -18023,7 +18096,7 @@
         <v>78</v>
       </c>
       <c r="AL136" t="s" s="2">
-        <v>537</v>
+        <v>549</v>
       </c>
       <c r="AM136" t="s" s="2">
         <v>78</v>

--- a/tiflow-erezept/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERP-PR-Task.xlsx
+++ b/tiflow-erezept/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERP-PR-Task.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2028-04-01</t>
+    <t>2026-06-30</t>
   </si>
   <si>
     <t>Publisher</t>
